--- a/artfynd/A 29068-2023 artfynd.xlsx
+++ b/artfynd/A 29068-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29068-2023 artfynd.xlsx
+++ b/artfynd/A 29068-2023 artfynd.xlsx
@@ -4291,10 +4291,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119846986</v>
+        <v>119847103</v>
       </c>
       <c r="B32" t="n">
-        <v>91832</v>
+        <v>91863</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4331,13 +4331,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>545261</v>
+        <v>545285</v>
       </c>
       <c r="R32" t="n">
-        <v>7009010</v>
+        <v>7008990</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119847103</v>
+        <v>119846986</v>
       </c>
       <c r="B33" t="n">
-        <v>91863</v>
+        <v>91832</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4409,21 +4409,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4433,13 +4433,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>545285</v>
+        <v>545261</v>
       </c>
       <c r="R33" t="n">
-        <v>7008990</v>
+        <v>7009010</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4495,10 +4495,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119847076</v>
+        <v>119847080</v>
       </c>
       <c r="B34" t="n">
-        <v>91863</v>
+        <v>91856</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4511,21 +4511,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4535,13 +4535,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>545244</v>
+        <v>545273</v>
       </c>
       <c r="R34" t="n">
-        <v>7008993</v>
+        <v>7008997</v>
       </c>
       <c r="S34" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4597,10 +4597,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119847080</v>
+        <v>119847076</v>
       </c>
       <c r="B35" t="n">
-        <v>91856</v>
+        <v>91863</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4613,21 +4613,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>545273</v>
+        <v>545244</v>
       </c>
       <c r="R35" t="n">
-        <v>7008997</v>
+        <v>7008993</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>

--- a/artfynd/A 29068-2023 artfynd.xlsx
+++ b/artfynd/A 29068-2023 artfynd.xlsx
@@ -4291,7 +4291,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119847103</v>
+        <v>119847076</v>
       </c>
       <c r="B32" t="n">
         <v>91863</v>
@@ -4331,13 +4331,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>545285</v>
+        <v>545244</v>
       </c>
       <c r="R32" t="n">
-        <v>7008990</v>
+        <v>7008993</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119847076</v>
+        <v>119847103</v>
       </c>
       <c r="B35" t="n">
         <v>91863</v>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>545244</v>
+        <v>545285</v>
       </c>
       <c r="R35" t="n">
-        <v>7008993</v>
+        <v>7008990</v>
       </c>
       <c r="S35" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>

--- a/artfynd/A 29068-2023 artfynd.xlsx
+++ b/artfynd/A 29068-2023 artfynd.xlsx
@@ -4189,10 +4189,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119847771</v>
+        <v>119847103</v>
       </c>
       <c r="B31" t="n">
-        <v>91883</v>
+        <v>91863</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4205,21 +4205,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545381</v>
+        <v>545285</v>
       </c>
       <c r="R31" t="n">
-        <v>7008846</v>
+        <v>7008990</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119847076</v>
+        <v>119846986</v>
       </c>
       <c r="B32" t="n">
-        <v>91863</v>
+        <v>91832</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4331,13 +4331,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>545244</v>
+        <v>545261</v>
       </c>
       <c r="R32" t="n">
-        <v>7008993</v>
+        <v>7009010</v>
       </c>
       <c r="S32" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119846986</v>
+        <v>119847080</v>
       </c>
       <c r="B33" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4409,21 +4409,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4433,13 +4433,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>545261</v>
+        <v>545273</v>
       </c>
       <c r="R33" t="n">
-        <v>7009010</v>
+        <v>7008997</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4495,10 +4495,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119847080</v>
+        <v>119847076</v>
       </c>
       <c r="B34" t="n">
-        <v>91856</v>
+        <v>91863</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4511,21 +4511,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2059</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4535,13 +4535,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>545273</v>
+        <v>545244</v>
       </c>
       <c r="R34" t="n">
-        <v>7008997</v>
+        <v>7008993</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4597,10 +4597,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119847103</v>
+        <v>119847771</v>
       </c>
       <c r="B35" t="n">
-        <v>91863</v>
+        <v>91883</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4613,21 +4613,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>545285</v>
+        <v>545381</v>
       </c>
       <c r="R35" t="n">
-        <v>7008990</v>
+        <v>7008846</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>

--- a/artfynd/A 29068-2023 artfynd.xlsx
+++ b/artfynd/A 29068-2023 artfynd.xlsx
@@ -4495,10 +4495,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119847076</v>
+        <v>119847771</v>
       </c>
       <c r="B34" t="n">
-        <v>91863</v>
+        <v>91883</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4511,21 +4511,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4535,13 +4535,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>545244</v>
+        <v>545381</v>
       </c>
       <c r="R34" t="n">
-        <v>7008993</v>
+        <v>7008846</v>
       </c>
       <c r="S34" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4597,10 +4597,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119847771</v>
+        <v>119847076</v>
       </c>
       <c r="B35" t="n">
-        <v>91883</v>
+        <v>91863</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4613,21 +4613,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>545381</v>
+        <v>545244</v>
       </c>
       <c r="R35" t="n">
-        <v>7008846</v>
+        <v>7008993</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>

--- a/artfynd/A 29068-2023 artfynd.xlsx
+++ b/artfynd/A 29068-2023 artfynd.xlsx
@@ -4495,10 +4495,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119847771</v>
+        <v>119847076</v>
       </c>
       <c r="B34" t="n">
-        <v>91883</v>
+        <v>91863</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4511,21 +4511,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4535,13 +4535,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>545381</v>
+        <v>545244</v>
       </c>
       <c r="R34" t="n">
-        <v>7008846</v>
+        <v>7008993</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4597,10 +4597,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119847076</v>
+        <v>119847771</v>
       </c>
       <c r="B35" t="n">
-        <v>91863</v>
+        <v>91883</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4613,21 +4613,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>545244</v>
+        <v>545381</v>
       </c>
       <c r="R35" t="n">
-        <v>7008993</v>
+        <v>7008846</v>
       </c>
       <c r="S35" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>

--- a/artfynd/A 29068-2023 artfynd.xlsx
+++ b/artfynd/A 29068-2023 artfynd.xlsx
@@ -4192,7 +4192,7 @@
         <v>119847103</v>
       </c>
       <c r="B31" t="n">
-        <v>91863</v>
+        <v>91881</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>119846986</v>
       </c>
       <c r="B32" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119847080</v>
+        <v>119847771</v>
       </c>
       <c r="B33" t="n">
-        <v>91856</v>
+        <v>91901</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4409,21 +4409,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2059</v>
+        <v>5448</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4433,13 +4433,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>545273</v>
+        <v>545381</v>
       </c>
       <c r="R33" t="n">
-        <v>7008997</v>
+        <v>7008846</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4495,10 +4495,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119847771</v>
+        <v>119847080</v>
       </c>
       <c r="B34" t="n">
-        <v>91883</v>
+        <v>91874</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4511,21 +4511,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5448</v>
+        <v>2059</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4535,13 +4535,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>545381</v>
+        <v>545273</v>
       </c>
       <c r="R34" t="n">
-        <v>7008846</v>
+        <v>7008997</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>119847076</v>
       </c>
       <c r="B35" t="n">
-        <v>91863</v>
+        <v>91881</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>

--- a/artfynd/A 29068-2023 artfynd.xlsx
+++ b/artfynd/A 29068-2023 artfynd.xlsx
@@ -4189,10 +4189,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119847103</v>
+        <v>119847080</v>
       </c>
       <c r="B31" t="n">
-        <v>91881</v>
+        <v>91874</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4205,21 +4205,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545285</v>
+        <v>545273</v>
       </c>
       <c r="R31" t="n">
-        <v>7008990</v>
+        <v>7008997</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119846986</v>
+        <v>119847076</v>
       </c>
       <c r="B32" t="n">
-        <v>91850</v>
+        <v>91881</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4331,13 +4331,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>545261</v>
+        <v>545244</v>
       </c>
       <c r="R32" t="n">
-        <v>7009010</v>
+        <v>7008993</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119847771</v>
+        <v>119846986</v>
       </c>
       <c r="B33" t="n">
-        <v>91901</v>
+        <v>91850</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4409,21 +4409,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4433,13 +4433,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>545381</v>
+        <v>545261</v>
       </c>
       <c r="R33" t="n">
-        <v>7008846</v>
+        <v>7009010</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4495,10 +4495,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119847080</v>
+        <v>119847771</v>
       </c>
       <c r="B34" t="n">
-        <v>91874</v>
+        <v>91901</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4511,21 +4511,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2059</v>
+        <v>5448</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4535,13 +4535,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>545273</v>
+        <v>545381</v>
       </c>
       <c r="R34" t="n">
-        <v>7008997</v>
+        <v>7008846</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119847076</v>
+        <v>119847103</v>
       </c>
       <c r="B35" t="n">
         <v>91881</v>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>545244</v>
+        <v>545285</v>
       </c>
       <c r="R35" t="n">
-        <v>7008993</v>
+        <v>7008990</v>
       </c>
       <c r="S35" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>

--- a/artfynd/A 29068-2023 artfynd.xlsx
+++ b/artfynd/A 29068-2023 artfynd.xlsx
@@ -4189,10 +4189,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119847080</v>
+        <v>119846986</v>
       </c>
       <c r="B31" t="n">
-        <v>91874</v>
+        <v>91850</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4205,21 +4205,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545273</v>
+        <v>545261</v>
       </c>
       <c r="R31" t="n">
-        <v>7008997</v>
+        <v>7009010</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119846986</v>
+        <v>119847771</v>
       </c>
       <c r="B33" t="n">
-        <v>91850</v>
+        <v>91901</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4409,21 +4409,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4361</v>
+        <v>5448</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4433,13 +4433,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>545261</v>
+        <v>545381</v>
       </c>
       <c r="R33" t="n">
-        <v>7009010</v>
+        <v>7008846</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4495,10 +4495,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119847771</v>
+        <v>119847103</v>
       </c>
       <c r="B34" t="n">
-        <v>91901</v>
+        <v>91881</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4511,21 +4511,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4535,13 +4535,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>545381</v>
+        <v>545285</v>
       </c>
       <c r="R34" t="n">
-        <v>7008846</v>
+        <v>7008990</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4597,10 +4597,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119847103</v>
+        <v>119847080</v>
       </c>
       <c r="B35" t="n">
-        <v>91881</v>
+        <v>91874</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4613,21 +4613,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>2059</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>545285</v>
+        <v>545273</v>
       </c>
       <c r="R35" t="n">
-        <v>7008990</v>
+        <v>7008997</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>

--- a/artfynd/A 29068-2023 artfynd.xlsx
+++ b/artfynd/A 29068-2023 artfynd.xlsx
@@ -4189,10 +4189,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119846986</v>
+        <v>119847771</v>
       </c>
       <c r="B31" t="n">
-        <v>91850</v>
+        <v>91901</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4205,21 +4205,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4361</v>
+        <v>5448</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545261</v>
+        <v>545381</v>
       </c>
       <c r="R31" t="n">
-        <v>7009010</v>
+        <v>7008846</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119847076</v>
+        <v>119847103</v>
       </c>
       <c r="B32" t="n">
         <v>91881</v>
@@ -4331,13 +4331,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>545244</v>
+        <v>545285</v>
       </c>
       <c r="R32" t="n">
-        <v>7008993</v>
+        <v>7008990</v>
       </c>
       <c r="S32" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119847771</v>
+        <v>119847076</v>
       </c>
       <c r="B33" t="n">
-        <v>91901</v>
+        <v>91881</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4409,21 +4409,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4433,13 +4433,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>545381</v>
+        <v>545244</v>
       </c>
       <c r="R33" t="n">
-        <v>7008846</v>
+        <v>7008993</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4495,10 +4495,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119847103</v>
+        <v>119846986</v>
       </c>
       <c r="B34" t="n">
-        <v>91881</v>
+        <v>91850</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4511,21 +4511,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4535,13 +4535,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>545285</v>
+        <v>545261</v>
       </c>
       <c r="R34" t="n">
-        <v>7008990</v>
+        <v>7009010</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>

--- a/artfynd/A 29068-2023 artfynd.xlsx
+++ b/artfynd/A 29068-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4697,6 +4697,309 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128620937</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91713</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>65</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Storbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>545536</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7008779</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128620850</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79673</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Storbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>545483</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7008932</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128620849</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78749</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>353</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Storbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>545473</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7008935</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29068-2023 artfynd.xlsx
+++ b/artfynd/A 29068-2023 artfynd.xlsx
@@ -4702,7 +4702,7 @@
         <v>128620937</v>
       </c>
       <c r="B36" t="n">
-        <v>91713</v>
+        <v>91719</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>128620850</v>
       </c>
       <c r="B37" t="n">
-        <v>79673</v>
+        <v>79677</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>128620849</v>
       </c>
       <c r="B38" t="n">
-        <v>78749</v>
+        <v>78753</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 29068-2023 artfynd.xlsx
+++ b/artfynd/A 29068-2023 artfynd.xlsx
@@ -4702,7 +4702,7 @@
         <v>128620937</v>
       </c>
       <c r="B36" t="n">
-        <v>91719</v>
+        <v>91725</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 29068-2023 artfynd.xlsx
+++ b/artfynd/A 29068-2023 artfynd.xlsx
@@ -4702,7 +4702,7 @@
         <v>128620937</v>
       </c>
       <c r="B36" t="n">
-        <v>91725</v>
+        <v>91727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>128620850</v>
       </c>
       <c r="B37" t="n">
-        <v>79677</v>
+        <v>79679</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>128620849</v>
       </c>
       <c r="B38" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 29068-2023 artfynd.xlsx
+++ b/artfynd/A 29068-2023 artfynd.xlsx
@@ -4702,7 +4702,7 @@
         <v>128620937</v>
       </c>
       <c r="B36" t="n">
-        <v>91727</v>
+        <v>91728</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 29068-2023 artfynd.xlsx
+++ b/artfynd/A 29068-2023 artfynd.xlsx
@@ -4702,7 +4702,7 @@
         <v>128620937</v>
       </c>
       <c r="B36" t="n">
-        <v>91728</v>
+        <v>91755</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>128620850</v>
       </c>
       <c r="B37" t="n">
-        <v>79679</v>
+        <v>79706</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>128620849</v>
       </c>
       <c r="B38" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 29068-2023 artfynd.xlsx
+++ b/artfynd/A 29068-2023 artfynd.xlsx
@@ -4702,7 +4702,7 @@
         <v>128620937</v>
       </c>
       <c r="B36" t="n">
-        <v>91755</v>
+        <v>91760</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>128620850</v>
       </c>
       <c r="B37" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>128620849</v>
       </c>
       <c r="B38" t="n">
-        <v>78782</v>
+        <v>78786</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 29068-2023 artfynd.xlsx
+++ b/artfynd/A 29068-2023 artfynd.xlsx
@@ -4702,7 +4702,7 @@
         <v>128620937</v>
       </c>
       <c r="B36" t="n">
-        <v>91760</v>
+        <v>91765</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 29068-2023 artfynd.xlsx
+++ b/artfynd/A 29068-2023 artfynd.xlsx
@@ -4702,7 +4702,7 @@
         <v>128620937</v>
       </c>
       <c r="B36" t="n">
-        <v>91765</v>
+        <v>91769</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>128620850</v>
       </c>
       <c r="B37" t="n">
-        <v>79710</v>
+        <v>79714</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>128620849</v>
       </c>
       <c r="B38" t="n">
-        <v>78786</v>
+        <v>78790</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 29068-2023 artfynd.xlsx
+++ b/artfynd/A 29068-2023 artfynd.xlsx
@@ -4702,7 +4702,7 @@
         <v>128620937</v>
       </c>
       <c r="B36" t="n">
-        <v>91769</v>
+        <v>91774</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>128620850</v>
       </c>
       <c r="B37" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>128620849</v>
       </c>
       <c r="B38" t="n">
-        <v>78790</v>
+        <v>78695</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 29068-2023 artfynd.xlsx
+++ b/artfynd/A 29068-2023 artfynd.xlsx
@@ -4702,7 +4702,7 @@
         <v>128620937</v>
       </c>
       <c r="B36" t="n">
-        <v>91776</v>
+        <v>91781</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>128620850</v>
       </c>
       <c r="B37" t="n">
-        <v>79619</v>
+        <v>79624</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>128620849</v>
       </c>
       <c r="B38" t="n">
-        <v>78695</v>
+        <v>78700</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 29068-2023 artfynd.xlsx
+++ b/artfynd/A 29068-2023 artfynd.xlsx
@@ -4702,7 +4702,7 @@
         <v>128620937</v>
       </c>
       <c r="B36" t="n">
-        <v>91781</v>
+        <v>91787</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>128620850</v>
       </c>
       <c r="B37" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         <v>128620849</v>
       </c>
       <c r="B38" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
